--- a/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F6BACB8-410C-45AE-BDDD-BAAB14406254}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{060C567F-3463-4C86-9719-4CFC1F382F52}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42DABEE8-C001-44D0-A85F-02D504FCBB83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59010B84-170F-4942-A057-FFD27AC82C94}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AE03381-5B25-461F-8281-EDC8FD9E31E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E23C7F9-7CD6-493F-89E2-038716D2BB86}"/>
 </file>